--- a/downloads/7.09.2026 to 11.09.2026.xlsx
+++ b/downloads/7.09.2026 to 11.09.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadashiv.bhimanna\Desktop\2026-27\Second Year Time Table\Weekly time table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4316BA3-41BD-49D9-B2DF-10EC41BABA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE706063-AF2D-40AE-BB7C-E53AD3F5B526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
   <si>
     <t>SVKM’s NMIMS - School of Business Managing, Hyderabad Campus
 TIME-TABLE  
@@ -139,12 +139,6 @@
 Dr Dileep Kumar</t>
   </si>
   <si>
-    <t>MC-Div A
-L07, 2nd floor
-Rescheduled class
-Dr Dileep Kumar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total Rewards
 L08, 2nd floor
 (Hybrid)
@@ -242,11 +236,6 @@
 Prof Neelima</t>
   </si>
   <si>
-    <t>Product Strategy
-L06, 2nd floor
-Prof Krishna</t>
-  </si>
-  <si>
     <t>Financial Derivatives
 L07, 2nd floor
 Prof. Narsimhulu</t>
@@ -256,6 +245,30 @@
   </si>
   <si>
     <t>Capston simulation exam</t>
+  </si>
+  <si>
+    <t>Pricing Strategy
+Rescheduled class
+L06, 2nd floor
+Dr Srividya Raghavan</t>
+  </si>
+  <si>
+    <t>AFSA_A
+Rescheduled class
+L07, 2nd floor
+Dr Narender Vunyale</t>
+  </si>
+  <si>
+    <t>BS Div B
+Rescheduled class
+L07, 2nd floor
+Dr Dileep Kumar</t>
+  </si>
+  <si>
+    <t>BS Div A
+5:30-6:00 pm
+L06, 2nd floor
+Dr Srividya Raghavan</t>
   </si>
 </sst>
 </file>
@@ -402,7 +415,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -835,6 +848,28 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -845,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -943,9 +978,6 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -982,12 +1014,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1036,6 +1062,31 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1066,14 +1117,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1081,28 +1126,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1396,23 +1435,23 @@
     <col min="4" max="4" width="21.140625" style="8" customWidth="1"/>
     <col min="5" max="5" width="6.42578125" customWidth="1"/>
     <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" customWidth="1"/>
     <col min="8" max="8" width="19.85546875" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
     </row>
     <row r="2" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1433,161 +1472,163 @@
       <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="68" t="s">
+      <c r="G2" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="69"/>
+      <c r="H2" s="75"/>
       <c r="I2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="85" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="78"/>
-      <c r="E3" s="71" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="82"/>
+      <c r="E3" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="85" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="77"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="61" t="s">
+      <c r="F3" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="81"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="58" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="62"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="59"/>
     </row>
-    <row r="5" spans="1:9" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="65" t="s">
+    <row r="5" spans="1:9" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="C5" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="83" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="72"/>
+      <c r="D5" s="87" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="78"/>
       <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="74"/>
-      <c r="I5" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="61"/>
+      <c r="I5" s="62" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="72.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="65"/>
+    <row r="6" spans="1:9" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="71"/>
       <c r="B6" s="13"/>
       <c r="C6" s="14"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="72"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="78"/>
       <c r="F6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="63" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="71" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="17"/>
-      <c r="C7" s="82" t="s">
-        <v>27</v>
+      <c r="C7" s="65" t="s">
+        <v>26</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="72"/>
+        <v>28</v>
+      </c>
+      <c r="E7" s="78"/>
       <c r="F7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="H7" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="59"/>
+      <c r="I7" s="56"/>
     </row>
-    <row r="8" spans="1:9" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="65"/>
+    <row r="8" spans="1:9" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="71"/>
       <c r="B8" s="13"/>
       <c r="C8" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="72"/>
+        <v>29</v>
+      </c>
+      <c r="E8" s="78"/>
       <c r="F8" s="23"/>
       <c r="G8" s="24" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
+      <c r="I8" s="7" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="63" x14ac:dyDescent="0.25">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="71" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="72"/>
-      <c r="F9" s="27" t="s">
+      <c r="E9" s="78"/>
+      <c r="F9" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="H9" s="21" t="s">
         <v>32</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>33</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="65"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="29"/>
-      <c r="C10" s="34"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="72"/>
+        <v>29</v>
+      </c>
+      <c r="E10" s="78"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="9" t="s">
@@ -1596,21 +1637,21 @@
       <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9" ht="63" x14ac:dyDescent="0.25">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="70" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="72"/>
-      <c r="F11" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="33"/>
+        <v>35</v>
+      </c>
+      <c r="E11" s="78"/>
+      <c r="F11" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="69"/>
       <c r="H11" s="9" t="s">
         <v>20</v>
       </c>
@@ -1618,88 +1659,84 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="65"/>
+    <row r="12" spans="1:9" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="71"/>
       <c r="B12" s="13"/>
-      <c r="C12" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="72"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="78"/>
+      <c r="F12" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="38" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="72"/>
-      <c r="F13" s="39" t="s">
+      <c r="D13" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="78"/>
+      <c r="F13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="41"/>
-      <c r="I13" s="42"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="41"/>
     </row>
     <row r="14" spans="1:9" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="65"/>
+      <c r="A14" s="71"/>
       <c r="B14" s="13"/>
-      <c r="C14" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="73"/>
+      <c r="C14" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="79"/>
       <c r="F14" s="7"/>
       <c r="G14" s="23"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="45"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="44"/>
     </row>
     <row r="15" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="70" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="10"/>
-      <c r="C15" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="48"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="52"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="49"/>
     </row>
     <row r="16" spans="1:9" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="65"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="56"/>
+      <c r="A16" s="71"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="53"/>
       <c r="F16" s="23"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="58"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1718,6 +1755,6 @@
     <mergeCell ref="C3:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="74" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="73" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>